--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25470899.23</v>
+        <v>27801.71</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>26991000.47</v>
+        <v>29460.92</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>34090288.19</v>
+        <v>37209.85</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>14280571.2</v>
+        <v>15587.37</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>39035499.79</v>
+        <v>42607.59</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>32654790</v>
+        <v>35642.99</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>24740100</v>
+        <v>27004.04</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>22979852</v>
+        <v>25082.71</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>28791000.42</v>
+        <v>31425.63</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>51995860</v>
+        <v>56753.94</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>60720801.96</v>
+        <v>66277.28999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1789,11 +1789,11 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>70300180.58</v>
+        <v>76733.27</v>
       </c>
     </row>
     <row r="23">
@@ -1854,11 +1854,11 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>104775930</v>
+        <v>114363.85</v>
       </c>
     </row>
     <row r="24">
@@ -1919,11 +1919,11 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>133472177.86</v>
+        <v>145686.06</v>
       </c>
     </row>
     <row r="25">
@@ -1980,11 +1980,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>16053100</v>
+        <v>17522.1</v>
       </c>
     </row>
     <row r="26">
@@ -2041,11 +2041,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>35042799.89</v>
+        <v>38249.53</v>
       </c>
     </row>
     <row r="27">
@@ -2102,11 +2102,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>69388571.56</v>
+        <v>75738.24000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2167,11 +2167,11 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>141371314.56</v>
+        <v>154308.04</v>
       </c>
     </row>
     <row r="29">
@@ -2228,11 +2228,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>69541999.45</v>
+        <v>75905.71000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2293,11 +2293,11 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>225568977.97</v>
+        <v>246210.53</v>
       </c>
     </row>
     <row r="31">
@@ -2358,11 +2358,11 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>134196300</v>
+        <v>146476.45</v>
       </c>
     </row>
     <row r="32">
@@ -2419,11 +2419,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>66793034</v>
+        <v>72905.19</v>
       </c>
     </row>
     <row r="33">
@@ -2480,11 +2480,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>43244600</v>
+        <v>47201.86</v>
       </c>
     </row>
     <row r="34">
@@ -2545,11 +2545,11 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>45762598.35</v>
+        <v>49950.28</v>
       </c>
     </row>
     <row r="35">
@@ -2606,11 +2606,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>57801870</v>
+        <v>63091.25</v>
       </c>
     </row>
     <row r="36">
@@ -2671,11 +2671,11 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>155560608</v>
+        <v>169795.78</v>
       </c>
     </row>
     <row r="37">
@@ -2732,11 +2732,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>19267290</v>
+        <v>21030.42</v>
       </c>
     </row>
     <row r="38">
@@ -2793,11 +2793,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>18890998.91</v>
+        <v>20619.69</v>
       </c>
     </row>
     <row r="39">
@@ -2854,11 +2854,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>16053100</v>
+        <v>17522.1</v>
       </c>
     </row>
     <row r="40">
@@ -2915,11 +2915,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>34261290</v>
+        <v>37396.5</v>
       </c>
     </row>
     <row r="41">
@@ -2976,11 +2976,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>23979690</v>
+        <v>26174.04</v>
       </c>
     </row>
     <row r="42">
@@ -3037,11 +3037,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>23999999.73</v>
+        <v>26196.21</v>
       </c>
     </row>
     <row r="43">
@@ -3098,11 +3098,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>24193890</v>
+        <v>26407.84</v>
       </c>
     </row>
     <row r="44">
@@ -3159,11 +3159,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>54383000</v>
+        <v>59359.52</v>
       </c>
     </row>
     <row r="45">
@@ -3220,11 +3220,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>38744020</v>
+        <v>42289.44</v>
       </c>
     </row>
     <row r="46">
@@ -3281,11 +3281,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>19246584</v>
+        <v>21007.82</v>
       </c>
     </row>
     <row r="47">
@@ -3342,11 +3342,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>22979852</v>
+        <v>25082.71</v>
       </c>
     </row>
     <row r="48">
@@ -3403,11 +3403,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>49480200</v>
+        <v>54008.07</v>
       </c>
     </row>
     <row r="49">
@@ -3464,11 +3464,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>27281799.58</v>
+        <v>29778.33</v>
       </c>
     </row>
     <row r="50">
@@ -3525,11 +3525,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>18869699.1</v>
+        <v>20596.44</v>
       </c>
     </row>
     <row r="51">
@@ -3590,11 +3590,11 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>78718500</v>
+        <v>85921.94</v>
       </c>
     </row>
     <row r="52">
@@ -3651,11 +3651,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>67068400</v>
+        <v>73205.75</v>
       </c>
     </row>
     <row r="53">
@@ -3712,11 +3712,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10160999.45</v>
+        <v>11090.82</v>
       </c>
     </row>
     <row r="54">
@@ -3773,11 +3773,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>19695452</v>
+        <v>21497.76</v>
       </c>
     </row>
     <row r="55">
@@ -3834,11 +3834,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>63173530</v>
+        <v>68954.47</v>
       </c>
     </row>
     <row r="56">
@@ -3899,11 +3899,11 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>531436626</v>
+        <v>580067.77</v>
       </c>
     </row>
     <row r="57">
@@ -3964,11 +3964,11 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>266289263.1</v>
+        <v>290657.08</v>
       </c>
     </row>
     <row r="58">
@@ -4025,11 +4025,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>72234904</v>
+        <v>78845.03999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4086,11 +4086,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>23387599.55</v>
+        <v>25527.77</v>
       </c>
     </row>
     <row r="60">
@@ -4147,11 +4147,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>54599580</v>
+        <v>59595.92</v>
       </c>
     </row>
     <row r="61">
@@ -4208,11 +4208,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>34518690.57</v>
+        <v>37677.46</v>
       </c>
     </row>
     <row r="62">
@@ -4269,11 +4269,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>17470800.55</v>
+        <v>19069.53</v>
       </c>
     </row>
     <row r="63">
@@ -4334,11 +4334,11 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>85949499.3</v>
+        <v>93814.64</v>
       </c>
     </row>
     <row r="64">
@@ -4395,11 +4395,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>23337090</v>
+        <v>25472.64</v>
       </c>
     </row>
     <row r="65">
@@ -4456,11 +4456,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>27191500</v>
+        <v>29679.76</v>
       </c>
     </row>
     <row r="66">
@@ -4517,11 +4517,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>15096899.3</v>
+        <v>16478.4</v>
       </c>
     </row>
     <row r="67">
@@ -4578,11 +4578,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>19695452</v>
+        <v>21497.76</v>
       </c>
     </row>
     <row r="68">
@@ -4643,11 +4643,11 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>256109122.5</v>
+        <v>279545.37</v>
       </c>
     </row>
     <row r="69">
@@ -4704,11 +4704,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>22412383.84</v>
+        <v>24463.31</v>
       </c>
     </row>
     <row r="70">
@@ -4765,11 +4765,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>40878558.7</v>
+        <v>44619.31</v>
       </c>
     </row>
     <row r="71">
@@ -4826,11 +4826,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>49485800.14</v>
+        <v>54014.19</v>
       </c>
     </row>
     <row r="72">
@@ -4887,11 +4887,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>54385380</v>
+        <v>59362.12</v>
       </c>
     </row>
     <row r="73">
@@ -4948,11 +4948,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>24339665</v>
+        <v>26566.96</v>
       </c>
     </row>
     <row r="74">
@@ -5009,11 +5009,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>16589433</v>
+        <v>18107.51</v>
       </c>
     </row>
     <row r="75">
@@ -5070,11 +5070,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>27774600</v>
+        <v>30316.22</v>
       </c>
     </row>
     <row r="76">
@@ -5131,11 +5131,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>29121252.79</v>
+        <v>31786.1</v>
       </c>
     </row>
     <row r="77">
@@ -5192,11 +5192,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>32654790</v>
+        <v>35642.99</v>
       </c>
     </row>
     <row r="78">
@@ -5253,11 +5253,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>30111900.42</v>
+        <v>32867.41</v>
       </c>
     </row>
     <row r="79">
@@ -5314,11 +5314,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>34261290</v>
+        <v>37396.5</v>
       </c>
     </row>
     <row r="80">
@@ -5379,11 +5379,11 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>100638300</v>
+        <v>109847.59</v>
       </c>
     </row>
     <row r="81">
@@ -5440,11 +5440,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>9623292</v>
+        <v>10503.91</v>
       </c>
     </row>
     <row r="82">
@@ -5501,11 +5501,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>34261290</v>
+        <v>37396.5</v>
       </c>
     </row>
     <row r="83">
@@ -5566,11 +5566,11 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>135660000</v>
+        <v>148074.09</v>
       </c>
     </row>
     <row r="84">
@@ -5627,11 +5627,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>59621563.26</v>
+        <v>65077.46</v>
       </c>
     </row>
     <row r="85">
@@ -5688,11 +5688,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>34518690.57</v>
+        <v>37677.46</v>
       </c>
     </row>
     <row r="86">
@@ -5753,11 +5753,11 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>86904034</v>
+        <v>94856.52</v>
       </c>
     </row>
     <row r="87">
@@ -5814,11 +5814,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>34261290</v>
+        <v>37396.5</v>
       </c>
     </row>
   </sheetData>
